--- a/fixtures/casos-sinteticos.xlsx
+++ b/fixtures/casos-sinteticos.xlsx
@@ -2477,7 +2477,7 @@
       <c r="F69" s="8" t="inlineStr"/>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>Esperado: FAIL + passos seguintes BLOCKED (funcionalidade inexistente)</t>
+          <t>Esperado: FAIL + passos seguintes BLOCKED com o provedor determinístico dos testes (clica no botão inexistente). Com o Claude real: NEEDS-REVIEW, pois o modelo informa que não encontra o elemento e o sistema não inventa um clique.</t>
         </is>
       </c>
     </row>
